--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,1023 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (German speaker)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683454003?gh_jid=7683454003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Culture Automation &amp; AI Project Manager</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7807064003?gh_jid=7807064003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4929769101?gh_jid=4929769101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Integrated Logistics Support</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913312101?gh_jid=4913312101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Maritime</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Militarisation</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913364101?gh_jid=4913364101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4880330101?gh_jid=4880330101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager – Physical Products</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4880207101?gh_jid=4880207101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager - Air</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Senior Lead - Distribution &amp; Logistics Transformation Project Manager</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta; Locust Grove; New York City</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8008632?gh_jid=8008632</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,12 +431,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -451,37 +458,2126 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Job Posted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Job Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Relevance Score</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Relevance Score (1-10)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>German Required</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (German speaker)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683454003?gh_jid=7683454003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>People &amp; Culture Automation &amp; AI Project Manager</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7807064003?gh_jid=7807064003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Lead - Distribution &amp; Logistics Transformation Project Manager</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta; Locust Grove; New York City</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8008632?gh_jid=8008632</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Events Program Manager</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/43842e76-d402-4e0e-a615-f410687e2a25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Events Program Manager</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/b62d4169-665d-45bb-b246-078f414f675e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>GRC Program Manager</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/4625019a-479a-41dd-bd5a-21847629772b</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>GRC Program Manager</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/def1573d-c2b6-42a7-963b-e13c3587b5e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>GRC Program Manager</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/e5869901-d578-4229-a856-47af76a8f39a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager - Security</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/b5362bc1-8a07-44e2-9ddc-cb4236aa0f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager - Security</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/b908b3e4-81f9-47b3-9088-ee8dd3932003</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager - Security</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/e76eaef3-f240-467d-8260-1d6d92ed5c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2021-05-07</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager (TPM)</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Palantir Zurich</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager (TPM) - Defense</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager, Product Legal</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Bellevue, Washington; Boston, Massachusetts; Seattle, Washington; Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8569993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Senior Field Technical Program Manager, Professional Services</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8554840002</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Public Sector</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8549259002</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Program Manager, Data for Good</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California; Seattle, Washington</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8385177002</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Reliability</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Bellevue, Washington; Seattle, Washington</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8445423002</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Staff Technical Program Manager - Reliability</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View, California; San Francisco, California</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8445428002</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Staff Program Manager, People M&amp;A</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>San Francisco, California</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8637368002</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Staff Technical Program Manager- Platform Features</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View, California; San Francisco, California</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8521198002</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -497,6 +504,1147 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -497,6 +504,1190 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140516224/senior-staff-technical-program-manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,950 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140516224/senior-staff-technical-program-manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,909 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140516224/senior-staff-technical-program-manager/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -485,6 +492,975 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Anaplan Project Manager Specialist</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140784689/anaplan-project-manager-specialist/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Program Manager, Transformation</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140783024/sr-program-manager-transformation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Program Manager, M&amp;A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140782575/sr-program-manager-ma/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -486,6 +500,975 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marvel Fusion</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager (f/m/x)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Fort Collins, CO</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager (Swedish speaker)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Customer Enablement Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>DeepDrive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://deepdrive.tech/job/2722900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NavVis</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>US Remote / Hybrid (NavVis Inc.)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Netcetera</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Anaplan Project Manager Specialist</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140784689/anaplan-project-manager-specialist/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Program Manager, Transformation</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140783024/sr-program-manager-transformation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ServiceNow Munich</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Program Manager, M&amp;A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.servicenow.com/jobs/744000140782575/sr-program-manager-ma/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -497,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -564,6 +1547,144 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Cognite</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4913354101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Cognite</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>UAE Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4926730101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Cognite</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>England, United Kingdom</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4913315101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -501,969 +501,930 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sr. Field Technical Program Manager, Forward Deployed Engineering</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8583037002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Marvel Fusion</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Technical Project Manager (f/m/x)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Fort Collins, CO</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/marvelfusion/jobs/4922855101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Lead Project Manager (Swedish speaker)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7781625003?gh_jid=7781625003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582991002</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Senior Customer Enablement Program Manager</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8535311002</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Meet Candice Meet Candice, Service Delivery Manager at Airbus Helicopters in Edinburgh, Australia</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://www.airbus.com/en/careers/life-at-airbus/airbus-faces/meet-candice</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Technical Programme Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4854142101</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Egym</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>(Senior) Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Germany, Munich</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://egym.jobs.personio.de/job/2724205</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DeepDrive</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Production Subproject Manager (m/f/x) Shanghai, China Full-time Permanent employee</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>https://deepdrive.tech/job/2722900</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>NavVis</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Reality Capture Project Manager (Fixed-Term Contract, 17 Months)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>US Remote / Hybrid (NavVis Inc.)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/navvis/jobs/4908378101</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Lead - Project Manager, Brand &amp; Product Assets</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Berlin; London; Zurich</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Program Manager -  Global Distributor-led Store Business</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Netcetera</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>IT Infrastructure Project Manager Skopje, North Macedonia</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>https://www.netcetera.com/careers/job-350DC93329-North-Macedonia-Skopje-IT-Infrastructure-Project-Manager.html</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>ServiceNow Munich</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Anaplan Project Manager Specialist</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>https://careers.servicenow.com/jobs/744000140784689/anaplan-project-manager-specialist/</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>ServiceNow Munich</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Sr. Program Manager, Transformation</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://careers.servicenow.com/jobs/744000140783024/sr-program-manager-transformation/</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>ServiceNow Munich</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Sr. Program Manager, M&amp;A</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>https://careers.servicenow.com/jobs/744000140782575/sr-program-manager-ma/</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Field Technical Program Manager</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Field Technical Program Manager</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Seoul, South Korea</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8598531002</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Field Technical Program Manager, Forward Deployed Engineering - LATAM</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Sao Paulo, Brazil</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8423289002</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Sr. Field Technical Program Manager, Forward Deployed Engineering - Canada</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8586460002</t>
         </is>
@@ -1548,138 +1509,135 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Cognite</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Project Manager</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4913354101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Cognite</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Senior Project Manager</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>UAE Abu Dhabi</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4926730101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Cognite</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Oslo</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Senior Project Manager</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>England, United Kingdom</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Unconfirmed</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/cognite/jobs/4913315101</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,18 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,11 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -491,112 +477,6 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Alpine Eagle</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>UnternehmerTUM</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>München Kreativquartier</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -433,9 +433,8 @@
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,15 +465,10 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>German Required</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
@@ -491,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -500,9 +494,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -538,15 +531,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>German Required</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,426 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,12 +42,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
-        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,10 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -478,426 +471,6 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Alpine Eagle</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ProGlove</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Senior Technical Project Manager</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Munich Office</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>https://proglove.jobs.personio.de/job/2732130</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>UnternehmerTUM</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>München Kreativquartier</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Berlin; London; Zurich</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Egym</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>(Senior) Project Manager (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Germany, Munich</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>https://egym.jobs.personio.de/job/2724205</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Program Manager -  Global Distributor-led Store Business</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>UnternehmerTUM</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>München Kreativquartier</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -482,245 +482,245 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
@@ -729,173 +729,208 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Lead - Project Manager, Brand &amp; Product Assets</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Berlin; London; Zurich</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Egym</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>(Senior) Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Germany, Munich</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://egym.jobs.personio.de/job/2724205</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Program Manager -  Global Distributor-led Store Business</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -727,35 +727,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dream Cities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global Top Picks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +51,12 @@
         <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,10 +70,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1005,4 +1013,134 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance Score (1-10)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Coupang</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Staff, Program Manager(CoupangEats Engineering)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8068604</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Coupang</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Staff, Technical Program Manager(CoupangEats Engineering)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8059231</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,12 @@
         <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,11 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -560,49 +567,49 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ProGlove</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Senior Technical Project Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich Office</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://proglove.jobs.personio.de/job/2732130</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>ProGlove</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -612,20 +619,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
+          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich Office</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
@@ -647,7 +654,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -660,14 +667,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -682,11 +689,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -695,19 +702,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -717,7 +724,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -725,24 +732,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -752,7 +759,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -760,174 +767,174 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>On Running</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Berlin; London; Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Egym</t>
+          <t>On Running</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(Senior) Project Manager (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Germany, Munich</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://egym.jobs.personio.de/job/2724205</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Program Manager -  Global Distributor-led Store Business</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>On Running</t>
+          <t>Egym</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+          <t>(Senior) Project Manager (m/w/d)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Germany, Munich</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>On Running</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -935,10 +942,80 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>
@@ -955,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1007,6 +1084,406 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Senior Social Impact Program Manager (Nonprofits)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8074357</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -567,35 +567,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
@@ -847,35 +847,35 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Field Technical Program Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
         </is>
@@ -1088,400 +1088,400 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Solarisbank</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Transformation and Project Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt; Berlin</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>GetYourGuide</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Car Fleet Program Manager</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Program Manager</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Senior Social Impact Program Manager (Nonprofits)</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8074357</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dream Cities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global Top Picks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_wildcard_history" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -604,4 +605,17 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -33,7 +33,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,9 +77,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -476,6 +497,531 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -487,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -542,6 +1088,406 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -553,7 +1499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -602,6 +1548,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Coupang</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Staff, Program Manager(CoupangEats Engineering)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8068604</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Coupang</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Seoul</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Staff, Technical Program Manager(CoupangEats Engineering)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8059231</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Careem</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/careem/jobs/8439069002?gh_jid=8439069002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -613,9 +1664,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8068604</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.jobs/en/jobs/?gh_jid=8059231</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/careem/jobs/8439069002?gh_jid=8439069002</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,636 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,6 +1184,286 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,6 +496,531 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -486,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,6 +1081,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -546,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -601,6 +1252,286 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,385 +497,385 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Lead - Project Manager, Brand &amp; Product Assets</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Berlin; London; Zurich</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Field Technical Program Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
         </is>
@@ -884,138 +884,173 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager - Hardware Engineering (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2711747</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Egym</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>(Senior) Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Germany, Munich</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://egym.jobs.personio.de/job/2724205</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Program Manager -  Global Distributor-led Store Business</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E17" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>
@@ -1082,105 +1117,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
@@ -1253,280 +1288,280 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Solarisbank</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Transformation and Project Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt; Berlin</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Trust &amp; Safety Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>GetYourGuide</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Car Fleet Program Manager</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Program Manager</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,6 +496,566 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Manager - Hardware Engineering (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2711747</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -486,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,6 +1116,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -546,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -601,6 +1287,286 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Program Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -497,560 +497,560 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Egym</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Technical Project Manager - Hardware Engineering (m/f/d)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Germany, Munich</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://egym.jobs.personio.de/job/2711747</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Lead - Project Manager, Brand &amp; Product Assets</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Berlin; London; Zurich</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Field Technical Program Manager</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Egym</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>(Senior) Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Germany, Munich</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://egym.jobs.personio.de/job/2724205</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Program Manager -  Global Distributor-led Store Business</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>On Running</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
         </is>
@@ -1117,105 +1117,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
@@ -1232,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1288,200 +1288,200 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Solarisbank</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Transformation and Project Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt; Berlin</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Trust &amp; Safety Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>GetYourGuide</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Car Fleet Program Manager</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
@@ -1490,78 +1490,118 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/8096040?gh_jid=8096040</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Program Manager</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1488,40 +1488,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/8096040?gh_jid=8096040</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -707,49 +707,45 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -759,7 +755,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -767,24 +763,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -794,7 +790,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -802,24 +798,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Egym</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -829,230 +825,1598 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Technical Project Manager - Hardware Engineering (m/f/d)</t>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Germany, Munich</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://egym.jobs.personio.de/job/2711747</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Berlin; London; Zurich</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Databricks Zurich</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Field Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Egym</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>(Senior) Project Manager (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Germany, Munich</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://egym.jobs.personio.de/job/2724205</t>
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Program Manager -  Global Distributor-led Store Business</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>On Running</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>HR Project Manager - Employee Engagement (M/F) / International Organization</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/hr-project-manager-employee-engagement-mf/ref/jn-072026-7058283</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Technical Project Manager - Hardware Engineering (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2711747</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lead - Project Manager, Brand &amp; Product Assets</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Berlin; London; Zurich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8083302?gh_jid=8083302</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Field Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8540665002</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Railway Maintenance Project Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/railway-maintenance-project-manager-ecm/ref/jn-022026-6949500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager - Wireless SoC Development (semiconductor)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/project-manager-wireless-soc-development-semiconductor/ref/jn-072026-7069295</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ingénieur / chef de projet amélioration continue (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/ing%C3%A9nieur-chef-de-projet-am%C3%A9lioration-continue-mfd/ref/jn-042026-7005833?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Chef de Projet Senior Équipements Électromécaniques - Infrastructures de Transport (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-senior-%C3%A9quipements-%C3%A9lectrom%C3%A9caniques/ref/jn-062026-7048961?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Chef de projet CVC (H/F)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-cvc-hf/ref/jn-062026-7051837?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Chef de Projet Aménagement</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-am%C3%A9nagement/ref/jn-072026-7071132?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Chef de projet CVC (H/F)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-cvc-hf/ref/jn-072026-7063818?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Chef de projet ouvrages hydrauliques (H/F)</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-ouvrages-hydrauliques-hf/ref/jn-102025-6873162?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Chef de projet environnement expérimenté (H/F)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-environnement-exp%C3%A9riment%C3%A9-hf/ref/jn-052026-7026368?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Chef de Projet Senior - RMO - Français/Allemand (H/F)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-senior-rmo-fran%C3%A7aisallemand-hf/ref/jn-122025-6910448?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Egym</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>(Senior) Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Germany, Munich</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://egym.jobs.personio.de/job/2724205</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/senior-project-manager-mwd/ref/jn-072026-7071967</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>INTERIM Projektleiter Cybersecurity (gn)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/interim-projektleiter-cybersecurity-gn/ref/jn-062026-7033799</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Rollout (m/w/d) E-Ladesäulen</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-rollout-mwd/ref/jn-072026-7057660</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Program Manager -  Global Distributor-led Store Business</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074409?gh_jid=8074409</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>On Running</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Senior Specialist - New Store Openings Project Manager, DMS</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/onrunning/jobs/8074401?gh_jid=8074401</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Werkstudent_in (m/w/d) Junior Project Manager</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2713170</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Senior Projektleiter (m/w/d) mit technischem Fokus</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/senior-projektleiter-mwd-mit-technischem-fokus/ref/jn-062026-7047981</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager / Projektsteuerer Hochbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-projektsteuerer-hochbau-mwd/ref/jn-072026-7065744</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-mwd/ref/jn-072026-7056677</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Baubranche (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-baubranche-mwd/ref/jn-082026-7076112</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) TGA</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-tga/ref/jn-072026-7073457</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter SHK (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-shk-mwd/ref/jn-072026-7073348</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Hochbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-hochbau-mwd/ref/jn-072026-7072141</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Reinraum (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-reinraum-mwd/ref/jn-062026-7041241</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Stadionbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-stadionbau-mwd/ref/jn-072026-7064146</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (m/w/d) Klinikbau</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-mwd-klinikbau/ref/jn-072026-7070410</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Bestand</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-bestand/ref/jn-072026-7070125</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Elektrotechnik (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-elektrotechnik-mwd/ref/jn-072026-7067742</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Museumsbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-museumsbau-mwd/ref/jn-072026-7064150</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter TGA (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-tga-mwd/ref/jn-072026-7060850</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) - Bauherrenvertretung</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-bauherrenvertretung/ref/jn-072026-7068001</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Hochbau</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hochbau/ref/jn-072026-7064291</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Projektleiter (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/senior-projektleiter-mwd/ref/jn-072026-7057579</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Schlüsselfertigbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-schl%C3%BCsselfertigbau-mwd/ref/jn-072026-7065738</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Hotelumbau</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hotelumbau/ref/jn-072026-7064123</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Wohnungsneubau</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-wohnungsneubau/ref/jn-072026-7062068</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>(Junior) Projektleiter (m/w/d) in der Projektsteuerung</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/junior-projektleiter-mwd-der-projektsteuerung/ref/jn-082026-7077143</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Hochbau</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-roh-und-schl%C3%BCsselfertigbau/ref/jn-082026-7077776</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Schlüsselfertigbau (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-schl%C3%BCsselfertigbau-mwd/ref/jn-072026-7059220</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) Hochbau</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hochbau/ref/jn-072026-7055719</t>
         </is>
       </c>
     </row>
@@ -1067,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1221,6 +2585,626 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Singapore</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>sap project manager | it project | it program</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>...| IT Project | IT Program in Singapore | Randstad Singapore contact...</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.com.sg/jobs/sap-project-manager-it-project-it-program_singapore_47160598/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Singapore</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>project manager (1-year contract)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>...Manager (1-Year Contract) in Singapore | Randstad Singapore contact...</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.com.sg/jobs/project-manager-1year-contract_singapore_47020691/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Singapore</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ai project manager/ pmo (transformation &amp; innovation strategy)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>...ion &amp; Innovation Strategy) in Singapore | Randstad Singapore contact...</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.com.sg/jobs/ai-project-manager-pmo-transformation-innovation-strategy_singapore_47116919/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Singapore</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>mas regulatory reporting project manager (1 year contract)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>...Manager (1 year contract) in Singapore River | Randstad Singapore co...</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.com.sg/jobs/mas-regulatory-reporting-project-manager-1-year-contract_singapore-river_47217372/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Randstad Singapore</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>it system analyst / business analyst (java) / project manager</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>...t (Java) / Project Manager in Singapore | Randstad Singapore contact...</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.randstad.com.sg/jobs/it-system-analyst-business-analyst-java-project-manager_singapore_47235650/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/it-pm-contract/ref/jn-072026-7061835</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager (WMS)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-wms/ref/jn-042026-7006140</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/technical-project-manager/ref/jn-042026-6985822</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/technical-project-manager/ref/jn-122025-6895859</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-railway-trackworks/ref/jn-012026-6920974</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-retail-project-fitting-out/ref/jn-032026-6975731</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager (CCTV) - Security firm</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-cctv-security-firm/ref/jn-042026-6985811</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager - Global System Supplier</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-global-system-supplier/ref/jn-052026-7012949</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager- Cyber Security</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-cyber-security-contract/ref/jn-052026-7013819</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-manager-digital-transformation-contract/ref/jn-052026-7016159</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/assistant-project-manager-interior-design-owner-side/ref/jn-082026-7076589</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Cloud Technical Project Manager (12 Months Contract)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/cloud-technical-project-manager-12-months-contract/ref/jn-072026-7063649</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Senior Project Manager (SEA) - Steel &amp; Facade Construction</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/senior-project-manager-sea-steel-facade-construction/ref/jn-062026-7051865</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/project-management-leader-data-centre-cooling-system/ref/jn-062026-7038781</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/assistant-manager-electrical-mechanical-data-centre/ref/jn-012026-6929105</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1232,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1328,42 +3312,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Wolt</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety Program Manager</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Senior Security Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
         </is>
       </c>
     </row>
@@ -1375,7 +3359,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GetYourGuide</t>
+          <t>Wolt</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1390,32 +3374,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Connectivity Partner Program Manager</t>
+          <t>Trust &amp; Safety Program Manager</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FREE NOW</t>
+          <t>GetYourGuide</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1430,32 +3414,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+          <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wolt</t>
+          <t>FREE NOW</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1470,7 +3454,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Car Fleet Program Manager</t>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1483,19 +3467,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Wolt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1510,7 +3494,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Car Fleet Program Manager</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1518,90 +3502,170 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://n26.com/en-eu/careers/positions/8096040?gh_jid=8096040</t>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/8096040?gh_jid=8096040</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Program Manager</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8076558</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -707,31 +707,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
@@ -843,155 +842,150 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>HR Project Manager - Employee Engagement (M/F) / International Organization</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/hr-project-manager-employee-engagement-mf/ref/jn-072026-7058283</t>
         </is>
@@ -1103,341 +1097,330 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Railway Maintenance Project Manager</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/railway-maintenance-project-manager-ecm/ref/jn-022026-6949500</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Project Manager - Wireless SoC Development (semiconductor)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/project-manager-wireless-soc-development-semiconductor/ref/jn-072026-7069295</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Ingénieur / chef de projet amélioration continue (m/f/d)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/ing%C3%A9nieur-chef-de-projet-am%C3%A9lioration-continue-mfd/ref/jn-042026-7005833?lang=en</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Chef de Projet Senior Équipements Électromécaniques - Infrastructures de Transport (m/f/d)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>3</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-senior-%C3%A9quipements-%C3%A9lectrom%C3%A9caniques/ref/jn-062026-7048961?lang=en</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Chef de projet CVC (H/F)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-cvc-hf/ref/jn-062026-7051837?lang=en</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Chef de Projet Aménagement</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-am%C3%A9nagement/ref/jn-072026-7071132?lang=en</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Chef de projet CVC (H/F)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-cvc-hf/ref/jn-072026-7063818?lang=en</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Chef de projet ouvrages hydrauliques (H/F)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-ouvrages-hydrauliques-hf/ref/jn-102025-6873162?lang=en</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Chef de projet environnement expérimenté (H/F)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-environnement-exp%C3%A9riment%C3%A9-hf/ref/jn-052026-7026368?lang=en</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Chef de Projet Senior - RMO - Français/Allemand (H/F)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/chef-de-projet-senior-rmo-fran%C3%A7aisallemand-hf/ref/jn-122025-6910448?lang=en</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
@@ -1479,93 +1462,90 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Senior Project Manager (m/w/d)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/senior-project-manager-mwd/ref/jn-072026-7071967</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>INTERIM Projektleiter Cybersecurity (gn)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/interim-projektleiter-cybersecurity-gn/ref/jn-062026-7033799</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Projektleiter Rollout (m/w/d) E-Ladesäulen</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" t="n">
         <v>2</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-rollout-mwd/ref/jn-072026-7057660</t>
         </is>
@@ -1677,746 +1657,753 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Senior Projektleiter (m/w/d) mit technischem Fokus</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/senior-projektleiter-mwd-mit-technischem-fokus/ref/jn-062026-7047981</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Projektmanager / Projektsteuerer Hochbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-projektsteuerer-hochbau-mwd/ref/jn-072026-7065744</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-mwd/ref/jn-072026-7056677</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Projektmanager Baubranche (m/w/d)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-baubranche-mwd/ref/jn-082026-7076112</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) TGA</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-tga/ref/jn-072026-7073457</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Projektleiter SHK (m/w/d)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-shk-mwd/ref/jn-072026-7073348</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Projektmanager Hochbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-hochbau-mwd/ref/jn-072026-7072141</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>Projektleiter Reinraum (m/w/d)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-reinraum-mwd/ref/jn-062026-7041241</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>Projektleiter Stadionbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-stadionbau-mwd/ref/jn-072026-7064146</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Projektmanager (m/w/d) Klinikbau</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-mwd-klinikbau/ref/jn-072026-7070410</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Bestand</t>
         </is>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-bestand/ref/jn-072026-7070125</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Projektleiter Elektrotechnik (m/w/d)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-elektrotechnik-mwd/ref/jn-072026-7067742</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Projektleiter Museumsbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-museumsbau-mwd/ref/jn-072026-7064150</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>Projektleiter TGA (m/w/d)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-tga-mwd/ref/jn-072026-7060850</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) - Bauherrenvertretung</t>
         </is>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-bauherrenvertretung/ref/jn-072026-7068001</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Hochbau</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hochbau/ref/jn-072026-7064291</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>(Senior) Projektleiter (m/w/d)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/senior-projektleiter-mwd/ref/jn-072026-7057579</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Projektleiter Schlüsselfertigbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-schl%C3%BCsselfertigbau-mwd/ref/jn-072026-7065738</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Hotelumbau</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hotelumbau/ref/jn-072026-7064123</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Wohnungsneubau</t>
         </is>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-wohnungsneubau/ref/jn-072026-7062068</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>(Junior) Projektleiter (m/w/d) in der Projektsteuerung</t>
         </is>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/junior-projektleiter-mwd-der-projektsteuerung/ref/jn-082026-7077143</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Hochbau</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-roh-und-schl%C3%BCsselfertigbau/ref/jn-082026-7077776</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>Projektleiter Schlüsselfertigbau (m/w/d)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-schl%C3%BCsselfertigbau-mwd/ref/jn-072026-7059220</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Projektleiter (m/w/d) Hochbau</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-hochbau/ref/jn-072026-7055719</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter (m/w/d) schlüsselfertiger Hochbau</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektleiter-mwd-schl%C3%BCsselfertiger-hochbau/ref/jn-082026-7078495</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2586,622 +2573,633 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Randstad Singapore</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>sap project manager | it project | it program</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...| IT Project | IT Program in Singapore | Randstad Singapore contact...</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.randstad.com.sg/jobs/sap-project-manager-it-project-it-program_singapore_47160598/</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Randstad Singapore</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>project manager (1-year contract)</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...Manager (1-Year Contract) in Singapore | Randstad Singapore contact...</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.randstad.com.sg/jobs/project-manager-1year-contract_singapore_47020691/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Randstad Singapore</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>ai project manager/ pmo (transformation &amp; innovation strategy)</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...ion &amp; Innovation Strategy) in Singapore | Randstad Singapore contact...</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.randstad.com.sg/jobs/ai-project-manager-pmo-transformation-innovation-strategy_singapore_47116919/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Randstad Singapore</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>mas regulatory reporting project manager (1 year contract)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...Manager (1 year contract) in Singapore River | Randstad Singapore co...</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.randstad.com.sg/jobs/mas-regulatory-reporting-project-manager-1-year-contract_singapore-river_47217372/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Randstad Singapore</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>it system analyst / business analyst (java) / project manager</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...t (Java) / Project Manager in Singapore | Randstad Singapore contact...</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.randstad.com.sg/jobs/it-system-analyst-business-analyst-java-project-manager_singapore_47235650/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/it-pm-contract/ref/jn-072026-7061835</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Project Manager (WMS)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-wms/ref/jn-042026-7006140</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Technical Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/technical-project-manager/ref/jn-042026-6985822</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Technical Project Manager</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/technical-project-manager/ref/jn-122025-6895859</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-railway-trackworks/ref/jn-012026-6920974</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-retail-project-fitting-out/ref/jn-032026-6975731</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Manager (CCTV) - Security firm</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-cctv-security-firm/ref/jn-042026-6985811</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Project Manager - Global System Supplier</t>
         </is>
       </c>
-      <c r="E17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-global-system-supplier/ref/jn-052026-7012949</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Project Manager- Cyber Security</t>
         </is>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-cyber-security-contract/ref/jn-052026-7013819</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-manager-digital-transformation-contract/ref/jn-052026-7016159</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Assistant Project Manager</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/assistant-project-manager-interior-design-owner-side/ref/jn-082026-7076589</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Cloud Technical Project Manager (12 Months Contract)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/cloud-technical-project-manager-12-months-contract/ref/jn-072026-7063649</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Senior Project Manager (SEA) - Steel &amp; Facade Construction</t>
         </is>
       </c>
-      <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/senior-project-manager-sea-steel-facade-construction/ref/jn-062026-7051865</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/project-management-leader-data-centre-cooling-system/ref/jn-062026-7038781</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Michael Page Singapore</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.michaelpage.com.sg/job-detail/assistant-manager-electrical-mechanical-data-centre/ref/jn-012026-6929105</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Michael Page Singapore</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Business Project Manager (12 months Contract - Extendable)</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>...al Services Jobs Returning to Singapore Work from Home or Hybrid Jobs...</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.com.sg/job-detail/business-project-manager-12-months-contract-extendable/ref/jn-082026-7078452</t>
         </is>
       </c>
     </row>
@@ -3312,40 +3310,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Senior Security Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
         </is>
@@ -3552,40 +3550,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,6 +496,472 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -486,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,6 +1022,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -546,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -601,6 +1193,326 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Senior Security Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,105 +497,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
@@ -604,359 +604,388 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
@@ -1023,105 +1052,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
@@ -1194,320 +1223,320 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Solarisbank</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Transformation and Project Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt; Berlin</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Senior Security Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Trust &amp; Safety Program Manager</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>GetYourGuide</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Car Fleet Program Manager</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -602,35 +602,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,9 +76,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -475,6 +496,507 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>UnternehmerTUM</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>München Kreativquartier</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -486,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,6 +1057,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Sales Dev AI Program Manager</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sr. Partner Delivery Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -546,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -601,6 +1228,363 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Solarisbank</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Senior Transformation and Project Manager (f/m/d)</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurt; Berlin</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Senior Security Program Manager</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Program Manager</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>GetYourGuide</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Connectivity Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Wolt</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Car Fleet Program Manager</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Absolute Software</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>...am Manager Revenue Operations Vancouver,
+            British Columbia...</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>https://jobs.jobvite.com/absolute/job/oSOtAfwt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Junior Commercial Operations Project Manager</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -497,175 +497,175 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
@@ -674,324 +674,353 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>UnternehmerTUM</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>München Kreativquartier</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
@@ -1058,105 +1087,105 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Databricks Zurich</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
@@ -1229,357 +1258,356 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Solarisbank</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Senior Transformation and Project Manager (f/m/d)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Frankfurt; Berlin</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/solarisbank/jobs/8554475002</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Senior Security Program Manager</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" t="n">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8102387</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Trust &amp; Safety Program Manager</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8014101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>GetYourGuide</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Connectivity Partner Program Manager</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/getyourguide/jobs/7976582</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Wolt</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Car Fleet Program Manager</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Absolute Software</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Vancouver</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Partner Program Manager</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>...am Manager Revenue Operations Vancouver,
             British Columbia...</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://jobs.jobvite.com/absolute/job/oSOtAfwt</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Catawiki</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Amsterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -672,35 +672,35 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
@@ -1023,6 +1023,41 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1087,44 +1122,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Databricks Zurich</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Sales Dev AI Program Manager</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager - Growth</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8055561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1139,7 +1174,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sr. Partner Delivery Manager</t>
+          <t>Sales Dev AI Program Manager</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -1152,7 +1187,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8582993002</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1209,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technical Program Manager</t>
+          <t>Sr. Partner Delivery Manager</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1186,6 +1221,41 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8458134002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Databricks Zurich</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8654620002</t>
         </is>
@@ -1202,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1418,54 +1488,54 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FREE NOW</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Senior Growth Program Manager</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://n26.com/en-eu/careers/positions/7930011?gh_jid=7930011</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wolt</t>
+          <t>FREE NOW</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1480,7 +1550,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Car Fleet Program Manager</t>
+          <t>(Senior) Technical Program Manager - M&amp;A Integration (m/f/d) - Berlin</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1493,29 +1563,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8029978</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Absolute Software</t>
+          <t>Wolt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Partner Program Manager</t>
+          <t>Car Fleet Program Manager</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1523,80 +1598,75 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/wolt/jobs/8034765</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Absolute Software</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Partner Program Manager</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>...am Manager Revenue Operations Vancouver,
             British Columbia...</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>https://jobs.jobvite.com/absolute/job/oSOtAfwt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Catawiki</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Amsterdam</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Junior Commercial Operations Project Manager</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Amsterdam, Netherlands</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N26</t>
+          <t>Catawiki</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Junior Commercial Operations Project Manager</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1604,12 +1674,92 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Amsterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/catawiki/jobs/7835396</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/8108374?gh_jid=8108374</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Strategy &amp; Program Manager, Scaled Account Management</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/adyen/jobs/8101509</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1027,35 +1027,35 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
@@ -1122,35 +1122,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager - Growth</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8055561</t>
         </is>
@@ -1272,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1488,40 +1488,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Senior Growth Program Manager</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/7930011?gh_jid=7930011</t>
         </is>
@@ -1724,42 +1724,82 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Strategy &amp; Program Manager, Scaled Account Management</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8101509</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>FREE NOW</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Junior Project Manager, New Businesses</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Berlin, Germany</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/freenow/jobs/8094419</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -532,84 +532,76 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter / Technical Project Manager Partner Managment (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>...Ulm, DE, 89077 Ulm, DE, 89077 Fürstenfeldbruck, DE, 82256 Ulm, DE, 89077 Ulm...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Technischer-Projektleiter-Technical-Project-Manager-Partner-Managment-%28mwd%29-89077/1355581755/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technische Programmleitung / Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5192 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technische-Programmleitung-Technical-Program-Manager-82256/1355585755/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Auterion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -619,32 +611,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ProGlove</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -654,27 +646,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Technical Project Manager</t>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Munich Office</t>
+          <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://proglove.jobs.personio.de/job/2732130</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -689,32 +681,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Project Manager Commercial (m/f/d)</t>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>ProGlove</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -724,32 +716,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
+          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Munich Office</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -759,27 +751,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -794,7 +786,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -807,19 +799,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -829,7 +821,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -837,29 +829,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -867,29 +864,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -897,29 +899,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -927,12 +929,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -949,11 +951,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -962,37 +964,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1011,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1022,29 +1024,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1052,12 +1049,108 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter / Technical Project Manager IVV / E2E Integration (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5194 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-Technical-Project-Manager-IVV-E2E-Integration-%28wmd%29-82256/1355582655/</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1764,40 +1857,76 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Boral</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Project Managers</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>...nds &amp; Snowy, NSW, Australia - Sydney, NSW, Australia About Boral J...</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.boral.com.au/jobs/project-managers-southern-highlands-snowy-nsw-australia-sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>FREE NOW</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Junior Project Manager, New Businesses</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Berlin, Germany</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/freenow/jobs/8094419</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -532,62 +532,60 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Technischer Projektleiter / Technical Project Manager Partner Managment (m/w/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...Ulm, DE, 89077 Ulm, DE, 89077 Fürstenfeldbruck, DE, 82256 Ulm, DE, 89077 Ulm...</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Technischer-Projektleiter-Technical-Project-Manager-Partner-Managment-%28mwd%29-89077/1355581755/</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technische Programmleitung / Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...equisition ID: 5192 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technische-Programmleitung-Technical-Program-Manager-82256/1355585755/</t>
         </is>
@@ -1124,31 +1122,30 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Technischer Projektleiter / Technical Project Manager IVV / E2E Integration (w/m/d)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>...equisition ID: 5194 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-Technical-Project-Manager-IVV-E2E-Integration-%28wmd%29-82256/1355582655/</t>
         </is>
@@ -1857,36 +1854,35 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Boral</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Sydney</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Project Managers</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>...nds &amp; Snowy, NSW, Australia - Sydney, NSW, Australia About Boral J...</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://careers.boral.com.au/jobs/project-managers-southern-highlands-snowy-nsw-australia-sydney</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -997,32 +997,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>IT Project Manager - FR / GE</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>IT-Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1040,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1052,7 +1053,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1070,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1082,29 +1083,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1112,29 +1108,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Technischer Projektleiter / Technical Project Manager IVV / E2E Integration (w/m/d)</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1142,12 +1143,73 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Technischer Projektleiter / Technical Project Manager IVV / E2E Integration (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>...equisition ID: 5194 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-Technical-Project-Manager-IVV-E2E-Integration-%28wmd%29-82256/1355582655/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Singapore &amp; Swiss Cities" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dream Cities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swiss Cities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Singapore &amp; Swiss Cities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dream Cities" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -532,9 +533,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Auterion</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,27 +550,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Technischer Projektleiter / Technical Project Manager Partner Managment (m/w/d)</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>...Ulm, DE, 89077 Ulm, DE, 89077 Fürstenfeldbruck, DE, 82256 Ulm, DE, 89077 Ulm...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Technischer-Projektleiter-Technical-Project-Manager-Partner-Managment-%28mwd%29-89077/1355581755/</t>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,32 +585,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Technische Programmleitung / Technical Program Manager</t>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>...equisition ID: 5192 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
+          <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technische-Programmleitung-Technical-Program-Manager-82256/1355585755/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Auterion</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -609,32 +620,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Technical Program Manager</t>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>ProGlove</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -644,27 +655,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
+          <t>Senior Technical Project Manager</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Munich Office</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -679,32 +690,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ProGlove</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -714,32 +725,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior Technical Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich Office</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://proglove.jobs.personio.de/job/2732130</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -749,27 +760,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Project Manager Commercial (m/f/d)</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -784,7 +795,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -797,19 +808,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>UnternehmerTUM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -819,7 +830,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -827,34 +838,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>München Kreativquartier</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -862,34 +868,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UnternehmerTUM</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Entrepreneurship &amp; Tech Education: Program Manager Education (f/m/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -897,29 +898,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>München Kreativquartier</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://unternehmertum.jobs.personio.de/job/2642556</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -927,12 +928,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
@@ -949,11 +950,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -962,254 +963,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Michael Page Germany</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>IT-Projektmanager (m/w/d)</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>IT Project Manager - FR / GE</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Technischer Projektleiter / Technical Project Manager IVV / E2E Integration (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>...equisition ID: 5194 Location: Fürstenfeldbruck, DE, 82256 Fürstenfeldbruck,...</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technischer-Projektleiter-Technical-Project-Manager-IVV-E2E-Integration-%28wmd%29-82256/1355582655/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
@@ -1219,6 +1068,66 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Job Posted</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Relevance Score (1-10)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1274,35 +1183,35 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Project Manager - Growth</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8055561</t>
         </is>
@@ -1418,13 +1327,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1640,40 +1549,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Senior Growth Program Manager</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Berlin</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>https://n26.com/en-eu/careers/positions/7930011?gh_jid=7930011</t>
         </is>
@@ -1876,117 +1785,42 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Adyen</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Strategy &amp; Program Manager, Scaled Account Management</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Amsterdam</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/adyen/jobs/8101509</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Boral</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Project Managers</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>...nds &amp; Snowy, NSW, Australia - Sydney, NSW, Australia About Boral J...</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://careers.boral.com.au/jobs/project-managers-southern-highlands-snowy-nsw-australia-sydney</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>FREE NOW</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Junior Project Manager, New Businesses</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Berlin, Germany</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/freenow/jobs/8094419</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -471,6 +478,569 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IT-Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
       </c>
     </row>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -482,563 +482,555 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>IT-Projektmanager (m/w/d)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
         <bgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,10 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,84 +629,76 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -709,27 +708,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -744,7 +743,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -757,24 +756,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -782,29 +786,34 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -812,29 +821,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -842,29 +851,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IT-Projektmanager (m/w/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -872,124 +881,120 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IT-Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>IT Project Manager - FR / GE</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -997,29 +1002,34 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1027,10 +1037,100 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
@@ -1047,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1096,6 +1196,37 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -629,62 +629,60 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Adnovum</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Senior IT Program / Project Manager Financial Services (a)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
@@ -951,31 +949,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
@@ -1197,31 +1194,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Angebots- und Projektmanager EW Systems (w/m/d)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...Angebots- und Projektmanager übernehmen Sie die Verantwortung fü...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Angebots-und-Projektmanager-EW-Systems-%28wmd%29-89077/1361578255/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -979,54 +979,50 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1034,29 +1030,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1064,12 +1065,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1087,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1099,7 +1100,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1117,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1128,6 +1129,36 @@
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -979,31 +979,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>4</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,49 +524,49 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>STARK Defence</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Prototyping Project Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://stark.jobs.personio.de/job/2744395</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Auterion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -584,12 +584,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
@@ -611,67 +611,72 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Adnovum</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -679,94 +684,85 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -776,27 +772,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,7 +807,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -824,24 +820,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -849,29 +850,34 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -879,29 +885,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -909,29 +915,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT-Projektmanager (m/w/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -939,19 +945,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -961,7 +967,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -969,29 +975,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+          <t>IT-Projektmanager (m/w/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -999,12 +1005,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
         </is>
       </c>
     </row>
@@ -1021,72 +1027,67 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1094,29 +1095,34 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1124,12 +1130,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1152,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1158,6 +1164,66 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,84 +524,80 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>STARK Defence</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Prototyping Project Manager</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://stark.jobs.personio.de/job/2744395</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Special Mission Aircraft</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5766 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Special-Mission-Aircraft-82256/1362042355/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Auterion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -611,7 +607,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -619,12 +615,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
@@ -646,67 +642,72 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adnovum</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+          <t>Projektleiter TLB und Informationssicherheit P-8A (w/m/d)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -714,200 +715,191 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>...equisition ID: 4852 Location: Fürstenfeldbruck, DE, 82256 Wurster Nordseeküs...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-TLB-und-Informationssicherheit-P-8A-%28wmd%29-82256/1361632455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Systems Engineer / Development Project Manager (DPM) (w/m/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...ntwicklungsarbeitspakete in Bezug auf Termine, Kosten und Quali...</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Systems-Engineer-Development-Project-Manager-%28DPM%29-%28wmd%29-89077/1362037255/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Special Mission Aircraft</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5807 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Special-Mission-Aircraft-82256/1362041355/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Misson UAS</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 5631 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Misson-UAS-82256/1362039955/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -915,29 +907,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -945,19 +942,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -967,7 +969,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -975,29 +977,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT-Projektmanager (m/w/d)</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1005,29 +1007,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1035,29 +1037,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1065,56 +1067,51 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IT-Projektmanager (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>Munich</t>
@@ -1122,27 +1119,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1152,37 +1149,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1190,29 +1187,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1220,10 +1222,100 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -559,31 +559,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Projektmanager Special Mission Aircraft</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...equisition ID: 5766 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Special-Mission-Aircraft-82256/1362042355/</t>
         </is>
@@ -785,111 +784,105 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Projektleiter Special Mission Aircraft</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...equisition ID: 5807 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Special-Mission-Aircraft-82256/1362041355/</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Projektmanager Misson UAS</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...equisition ID: 5631 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Misson-UAS-82256/1362039955/</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -899,20 +892,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
@@ -934,7 +927,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -947,14 +940,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -969,7 +962,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -982,24 +975,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1007,12 +1005,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1027,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1042,24 +1040,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1067,12 +1065,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1087,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IT-Projektmanager (m/w/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1102,14 +1100,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1119,7 +1117,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Project Lead Police Helicopters (w/m/d)</t>
+          <t>IT-Projektmanager (m/w/d)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1127,29 +1125,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
+          <t>https://www.michaelpage.de/job-detail/it-projektmanager-mwd/ref/jn-082026-7082683</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+          <t>Project Lead Police Helicopters (w/m/d)</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1157,64 +1155,59 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+          <t>...equisition ID: 5556 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Project-Lead-Police-Helicopters-%28wmd%29-82256/1361623855/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Projektmanager (w/m/d) für Leistungstransformatoren</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>...m Power Transformers Europe Clusters (MPT) in Deutschland, Österr...</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Projektmanager-w-m-d-f-r-Leistungstransformatoren/301604</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Entrix</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1222,29 +1215,34 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1252,12 +1250,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1272,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Data &amp; AI Project Manager - 6 months mission</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1287,7 +1285,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1302,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Data &amp; AI Project Manager - 6 months mission</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1316,6 +1314,36 @@
         </is>
       </c>
       <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/data-ai-project-manager-6-months-mission/ref/jn-062026-7042466</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,604 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>STARK Defence</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Prototyping Project Manager</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://stark.jobs.personio.de/job/2744395</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Entrix</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Junior Portfolio Manager (d/f/m)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Aeromaritime Systembau GmbH</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +1146,99 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2771</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -489,598 +489,590 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>STARK Defence</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Prototyping Project Manager</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://stark.jobs.personio.de/job/2744395</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Projektmanager Selfprotection Ground (w/m/d)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Adnovum</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Senior IT Program / Project Manager Financial Services (a)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
@@ -1147,93 +1139,90 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2999</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Projektmanager:in Verkehr</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -759,37 +759,33 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
         </is>
       </c>
     </row>
@@ -811,7 +807,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -824,14 +820,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,7 +842,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -859,24 +855,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -884,29 +885,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -914,94 +915,95 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Space (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1009,29 +1011,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1039,12 +1041,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1063,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1073,6 +1075,66 @@
         </is>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -759,31 +759,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
         </is>
@@ -955,31 +954,30 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -559,49 +559,49 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Auterion</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Technical Program Manager</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>STARK Defence</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager - Battery IPT (all genders)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://stark.jobs.personio.de/job/2770927</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Isar Aerospace</t>
+          <t>Auterion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Senior Program Manager Launch Services (m/f/d)</t>
+          <t>Technical Program Manager</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -619,12 +619,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
@@ -646,67 +646,72 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adnovum</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -714,64 +719,64 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -779,89 +784,80 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -889,24 +885,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -914,19 +915,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -936,7 +942,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -944,19 +950,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -966,7 +972,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -974,24 +980,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1001,67 +1002,72 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1069,29 +1075,29 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1099,12 +1105,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1127,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1133,6 +1139,66 @@
         </is>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -559,35 +559,35 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>STARK Defence</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Project Manager - Battery IPT (all genders)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://stark.jobs.personio.de/job/2770927</t>
         </is>
@@ -824,31 +824,30 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -699,49 +699,50 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager Integration IAMD (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4098 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integration-IAMD-%28wmd%29-82256/1348113655/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adnovum</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -749,64 +750,64 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -814,12 +815,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
@@ -836,7 +837,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -844,47 +845,42 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -906,7 +902,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -919,14 +915,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +937,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -954,24 +950,29 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -979,29 +980,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1009,29 +1010,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1039,64 +1040,64 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Projektleiter Space (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1104,29 +1105,29 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1134,12 +1135,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1157,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1169,7 +1170,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1187,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1198,6 +1199,36 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -699,31 +699,30 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Projektmanager Integration IAMD (w/m/d)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>...equisition ID: 4098 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integration-IAMD-%28wmd%29-82256/1348113655/</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1244,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1294,32 +1294,33 @@
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ILF Beratende Ingenieure GmbH</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bern</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Projektleiter:in im Bereich Infrastruktur</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://www.ilf.com/job/?id=2876</t>
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager (w/m/d) Manufacturing Network</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...onentenlieferungen aus dem globalen „Large Steam and Syncon“ Fer...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-w-m-d-Manufacturing-Network/302293</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1350,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.ilf.com/job/?id=2999</t>
+          <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1367,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Projektmanager:in Verkehr</t>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1374,10 +1375,40 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1294,31 +1294,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Basel</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (w/m/d) Manufacturing Network</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...onentenlieferungen aus dem globalen „Large Steam and Syncon“ Fer...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-w-m-d-Manufacturing-Network/302293</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -789,54 +789,55 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Warning Sensors (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 6046 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Warning-Sensors-%28wmd%29-82024/1363009155/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -844,12 +845,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
@@ -866,7 +867,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -874,47 +875,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -936,7 +932,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -949,14 +945,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -971,7 +967,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -984,24 +980,29 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1009,29 +1010,29 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1039,29 +1040,29 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1069,94 +1070,95 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Projektleiter Space (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Avionik/Selbstschutzsysteme (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 6045 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-AvionikSelbstschutzsysteme-%28wmd%29-82024/1363014555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Project Manager</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1164,29 +1166,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1194,12 +1196,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1218,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1228,6 +1230,66 @@
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -729,62 +729,64 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>(Teil-)Projektleiter Counter-UAS Requirements &amp; Design (m/w/d)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 6137 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-%28Teil-%29Projektleiter-Counter-UAS-Requirements-&amp;-Design-%28mwd%29-82256/1363116955/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Adnovum</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Senior IT Program / Project Manager Financial Services (a)</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Technical Project Lead / Solution Architect c-UAS (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 6166 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technical-Project-Lead-Solution-Architect-c-UAS-%28wmd%29-82256/1363123255/</t>
         </is>
       </c>
     </row>
@@ -802,85 +804,80 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Projektleiter Warning Sensors (w/m/d)</t>
+          <t>Technical Project Lead / Solution Architect c-UAS (w/m/d)</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 6167 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technical-Project-Lead-Solution-Architect-c-UAS-%28wmd%29-82256/1363124255/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Projektmanager Selfprotection Ground (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 6046 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Warning-Sensors-%28wmd%29-82024/1363009155/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5</v>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+          <t>...equisition ID: 1850 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektmanager-Selfprotection-Ground-%28wmd%29-82024/1325906955/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Adnovum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
@@ -897,142 +894,137 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+          <t>Projektleiter Warning Sensors (w/m/d)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+          <t>...equisition ID: 6046 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-Warning-Sensors-%28wmd%29-82024/1363009155/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Lead Project Manager</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Michael Page Switzerland</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Zurich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1040,19 +1032,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1062,7 +1059,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1070,29 +1067,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1100,55 +1102,49 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Projektleiter Avionik/Selbstschutzsysteme (w/m/d)</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>...equisition ID: 6045 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-AvionikSelbstschutzsysteme-%28wmd%29-82024/1363014555/</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Entrix</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1158,97 +1154,102 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Junior Portfolio Manager (d/f/m)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Hensoldt</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Projektleiter Avionik/Selbstschutzsysteme (w/m/d)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...equisition ID: 6045 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-AvionikSelbstschutzsysteme-%28wmd%29-82024/1363014555/</t>
         </is>
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Entrix</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Junior Portfolio Manager (d/f/m)</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1256,29 +1257,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1286,10 +1287,100 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -729,93 +729,90 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>(Teil-)Projektleiter Counter-UAS Requirements &amp; Design (m/w/d)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>...equisition ID: 6137 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-%28Teil-%29Projektleiter-Counter-UAS-Requirements-&amp;-Design-%28mwd%29-82256/1363116955/</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Technical Project Lead / Solution Architect c-UAS (w/m/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>...equisition ID: 6166 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technical-Project-Lead-Solution-Architect-c-UAS-%28wmd%29-82256/1363123255/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Technical Project Lead / Solution Architect c-UAS (w/m/d)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>7</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>...equisition ID: 6167 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Technical-Project-Lead-Solution-Architect-c-UAS-%28wmd%29-82256/1363124255/</t>
         </is>
@@ -912,54 +909,59 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Hensoldt</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -967,12 +969,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
@@ -989,7 +991,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+          <t>Projektmanager Integrated Product Support Sanität (w/m/d)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -997,47 +999,42 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>...equisition ID: 4938 Location: Fürstenfeldbruck, DE, 82256 Bonn, DE, 53175 Ko...</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektmanager-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362310855/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Projektleiter Integrated Product Support Sanität (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>...equisition ID: 4940 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Integrated-Product-Support-Sanit%C3%A4t-%28wmd%29-82256/1362543455/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1056,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1072,14 +1069,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1094,7 +1091,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1107,24 +1104,29 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1132,29 +1134,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1162,29 +1164,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Projektleiter Space (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1192,12 +1194,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1211,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Projektleiter Avionik/Selbstschutzsysteme (w/m/d)</t>
+          <t>Projektleiter Space (w/m/d)</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1222,64 +1224,64 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>...ationaler Kundenprojekte in Bezug auf elektro-optische Systeme...</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Oberkochen-Projektleiter-Space-%28wmd%29-73447/1362330955/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Projektleiter Avionik/Selbstschutzsysteme (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>...equisition ID: 6045 Location: Taufkirchen, DE, 82024 Company: HENSOLDT...</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Taufkirchen-Projektleiter-AvionikSelbstschutzsysteme-%28wmd%29-82024/1363014555/</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Entrix</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Junior Portfolio Manager (d/f/m)</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://entrix.jobs.personio.de/job/2663715</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Aeromaritime Systembau GmbH</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1287,29 +1289,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://entrix.jobs.personio.de/job/2663715</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1317,12 +1319,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1341,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1352,7 +1354,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1371,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1381,6 +1383,36 @@
         </is>
       </c>
       <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+        <bgColor rgb="00FDE68A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +69,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -474,6 +488,1059 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Alpine Eagle</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mission Operations Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ARX Robotics</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Program Manager (m,f,d)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4961248101</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Project Manager</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4862537101?gh_jid=4862537101</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager – Physical Products</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4880207101?gh_jid=4880207101</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944089101?gh_jid=4944089101</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Militarisation</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913364101?gh_jid=4913364101</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Auterion</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Technical Program Manager</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Senior Program Manager Launch Services (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Associate Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Berlin; Munich</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944070101?gh_jid=4944070101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager - Integrated Logistics Support</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4913312101?gh_jid=4913312101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Land</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4944213101?gh_jid=4944213101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Senior Project Manager - Ground Systems (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Adnovum</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior IT Program / Project Manager Financial Services (a)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ProGlove</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Project Manager</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Munich Office</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://proglove.jobs.personio.de/job/2732130</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Programme Manager - Space</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Senior Programme Manager - Maritime</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Munich - Berlin</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>(Senior) Programme Manager Mission Systems</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Helsing</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Technical Programme Manager - Air</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Isar Aerospace</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager Commercial (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Customer Engagement Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Customer Success Program Manager - Scale Team</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Lead Project Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Munich, Germany</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager / Product Owner</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Germany</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Projektmanager SAP Einführung (gn)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Aeromaritime Systembau GmbH</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager - FR / GE</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -485,7 +1552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -534,6 +1601,99 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2876</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Projektleiter:in im Bereich Infrastruktur</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ILF Beratende Ingenieure GmbH</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bern</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Projektmanager:in Verkehr</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ilf.com/job/?id=2771</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,929 +489,925 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Alpine Eagle</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Karlsruhe, Baden-Württemberg, Germany, München, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/alpineeagle/jobs/4699459101</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Mission Operations Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4953147101</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ARX Robotics</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Program Manager (m,f,d)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/arxroboticsgmbh/jobs/4961248101</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Procurement Project Manager</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4862537101?gh_jid=4862537101</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>Senior Project Manager – Physical Products</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4880207101?gh_jid=4880207101</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944089101?gh_jid=4944089101</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Militarisation</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4913364101?gh_jid=4913364101</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Auterion</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Technical Program Manager</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://auterion.com/company/careers-open-position/8470060002?gh_jid=8470060002</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Senior Program Manager Launch Services (m/f/d)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4936418101</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Associate Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Berlin; Munich</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944070101?gh_jid=4944070101</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager - Integrated Logistics Support</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" t="n">
         <v>8</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4913312101?gh_jid=4913312101</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Land</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4944213101?gh_jid=4944213101</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Senior Project Manager - Ground Systems (m/f/d)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4756747101</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Adnovum</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Senior IT Program / Project Manager Financial Services (a)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>...inancial Services (a) 80-100% Zurich What you're going to do Ready...</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>https://careers.adnovum.com/job/Zurich-Senior-IT-Program-Project-Manager-Financial-Services-%28a%29/1164878455/</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ProGlove</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Senior Technical Project Manager</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Munich Office</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>https://proglove.jobs.personio.de/job/2732130</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Programme Manager</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4636978101?gh_jid=4636978101</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Programme Manager - Space</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" t="n">
         <v>6</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4942502101?gh_jid=4942502101</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Senior Programme Manager - Maritime</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Munich - Berlin</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4875025101?gh_jid=4875025101</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>(Senior) Programme Manager Mission Systems</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4968741101?gh_jid=4968741101</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Helsing</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Technical Programme Manager - Air</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" t="n">
         <v>6</v>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://helsing.ai/jobs/4865991101?gh_jid=4865991101</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Isar Aerospace</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Celonis</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Lead Project Manager</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Munich, Germany</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>ETH Zurich</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" t="n">
         <v>4</v>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Michael Page Germany</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" t="n">
         <v>4</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
@@ -1421,121 +1417,148 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
           <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Project Manager (m/f/d)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E31" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E32" t="n">
         <v>3</v>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E33" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>
@@ -1552,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1605,90 +1628,118 @@
       <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Basel</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2876</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Projektleiter:in im Bereich Infrastruktur</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>...Kabelinfrastrukturprojekten) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2999</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
-      <c r="B4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>ILF Beratende Ingenieure GmbH</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Projektmanager:in Verkehr</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>...städtische Verkehrssysteme) übernehmen. Sie werden mit der Leit...</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.ilf.com/job/?id=2771</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -1414,31 +1414,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Hensoldt</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Projektleiter ILS/IPS (w/m/d)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
@@ -1625,31 +1624,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Basel</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Project Manager (f/m/d) – Service &amp; Repair (Gas Turbine Components)</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>...gungssicherheit. Steuerung globaler Lieferketten einschließlich...</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Project-Manager-f-m-d-Service-Repair-Gas-Turbine-Components/303134</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1184,49 +1184,45 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Isar Aerospace</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Project Manager Commercial (m/f/d)</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Energy</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Real Estate Project Manager (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>...eichung der Projektziele in Bezug auf Qualität, Budget und Zeit...</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Real-Estate-Project-Manager-w-m-d/302381</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>Isar Aerospace</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1236,62 +1232,58 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
+          <t>Project Manager Commercial (m/f/d)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Ottobrunn, Bavaria, Germany; Parsdorf, Bavaria, Germany</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+          <t>https://job-boards.eu.greenhouse.io/isaraerospace/jobs/4949469101</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Customer Success Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Munich Re</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1306,7 +1298,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1319,24 +1311,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1344,29 +1341,34 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1374,29 +1376,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1404,19 +1406,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1426,7 +1428,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1434,19 +1436,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1456,108 +1458,230 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bundesamt fur Informatik BIT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>GAF Geospatial GmbH</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Junior Project Manager – Software Development and Operations</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Aeromaritime Systembau GmbH</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Project Manager (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Project Manager</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E35" t="n">
         <v>3</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
+    <row r="36">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E36" t="n">
         <v>3</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
+    <row r="37">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Senior Hands-On IT Project Manager - Integration</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E37" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1184,31 +1184,30 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Siemens Energy</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Real Estate Project Manager (w/m/d)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>...eichung der Projektziele in Bezug auf Qualität, Budget und Zeit...</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Real-Estate-Project-Manager-w-m-d/302381</t>
         </is>
@@ -1250,68 +1249,63 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Munich Re</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Project Manager - SAP SuccessFactors (m/f/d)*</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>...AP SuccessFactors (m/f/d)* in Munich at Munich Re Skip to main con...</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://careers.munichre.com/en/job/munich/project-manager-sap-successfactors-m-f-d/3342/44462004480</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Celonis</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Customer Engagement Program Manager - Scale Team</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Munich, Germany</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Manager</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1327,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Customer Success Program Manager - Scale Team</t>
+          <t>Customer Engagement Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1346,14 +1340,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823007003?gh_jid=7823007003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1368,7 +1362,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lead Project Manager</t>
+          <t>Customer Success Program Manager - Scale Team</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1381,24 +1375,29 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7823005003?gh_jid=7823005003</t>
         </is>
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
+          <t>Lead Project Manager</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1406,19 +1405,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
+          <t>https://job-boards.greenhouse.io/celonis/jobs/7683452003?gh_jid=7683452003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1428,7 +1427,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IT Project Manager / Product Owner</t>
+          <t>Projektleiter:in IT (w/m/d) 60%-100%, Zürich, befristet 08.09.2026                 |                 Informatikdienste</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1436,29 +1435,29 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...eiter:in IT (w/m/d) 60%-100%, Zürich, befristet print Drucken An d...</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
+          <t>https://jobs.ethz.ch/job/view/JOPG_ethz_Mv6A7zxfE2ogt3097w</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>Michael Page Germany</t>
+          <t>Michael Page Switzerland</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Zurich</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Projektmanager SAP Einführung (gn)</t>
+          <t>IT Project Manager / Product Owner</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1466,29 +1465,29 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+          <t>https://www.michaelpage.ch/job-detail/it-project-manager-product-owner/ref/jn-072026-7053211</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hensoldt</t>
+          <t>Michael Page Germany</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Projektleiter ILS/IPS (w/m/d)</t>
+          <t>Projektmanager SAP Einführung (gn)</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1496,81 +1495,79 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>...üsseldorf Frankfurt Stuttgart München Alle Büros Kontakt Kontakt au...</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.de/job-detail/projektmanager-sap-einf%C3%BChrung-gn/ref/jn-072026-7074884</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Projektleiter ILS/IPS (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>...für Produkte und Projekte des zugehörigen Programmbereichs Ange...</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://jobs.hensoldt.net/job/Ulm-Projektleiter-ILSIPS-%28wmd%29-89077/1363566455/</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Bundesamt fur Informatik BIT</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Projektleiter/-in für grosskalibrige Munition Bundesamt für Rüstung armasuisse Bern | 100%</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E33" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>...hschulabschluss (Bachelor) vorzugsweise in Elektrotechnik oder...</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://jobs.admin.ch/offene-stellen/projektleiter-in-fuer-grosskalibrige-munition/54119111-a980-43d3-8597-e9fd348e9a01</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>GAF Geospatial GmbH</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Junior Project Manager – Software Development and Operations</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aeromaritime Systembau GmbH</t>
+          <t>GAF Geospatial GmbH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1580,37 +1577,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Project Manager (m/f/d)</t>
+          <t>Junior Project Manager – Software Development and Operations</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
+          <t>...r team at our headquarters in Munich , we are looking for a motiva...</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
+          <t>https://careers.gaf.de/junior-project-manager-software-development-and-operations/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>Michael Page Switzerland</t>
+          <t>Aeromaritime Systembau GmbH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Zurich</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Project Manager (m/f/d)</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1618,12 +1615,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+          <t>...ement Location: Neufahrn near Freising, Germany Start Date: As soon...</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/jobs/project-manager</t>
+          <t>https://aeromaritimegroup.com/jobs/project-manager-m-f-d/</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1637,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IT Project Manager - FR / GE</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1653,7 +1650,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+          <t>https://www.michaelpage.ch/jobs/project-manager</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1667,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Senior Hands-On IT Project Manager - Integration</t>
+          <t>IT Project Manager - FR / GE</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1682,6 +1679,36 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.michaelpage.ch/fr/job-detail/it-project-manager-fr-ge/ref/jn-062026-7044696?lang=en</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Michael Page Switzerland</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Senior Hands-On IT Project Manager - Integration</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
         </is>

--- a/data/job_tracker.xlsx
+++ b/data/job_tracker.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1279,31 +1279,30 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Michael Page Switzerland</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Zurich</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>IT Project Manager</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>...s Our offices Geneva Lausanne Zurich All Switzerland Talent Trends...</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/it-project-manager/ref/jn-092026-7100459</t>
         </is>
@@ -1711,6 +1710,37 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>https://www.michaelpage.ch/job-detail/senior-hands-it-project-manager-integration/ref/jn-052026-7008447</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Hensoldt</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Projektleiter Software Defined Defence (SDD) (w/m/d)</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>...equisition ID: 3422 Location: Fürstenfeldbruck, DE, 82256 Company: ESG Elekt...</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://jobs.hensoldt.net/job/F%C3%BCrstenfeldbruck-Projektleiter-Software-Defined-Defence-%28SDD%29-%28wmd%29-82256/1352828255/</t>
         </is>
       </c>
     </row>
